--- a/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">1962</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">4982</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">Beta 22.79</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.222</t>
+    <t xml:space="preserve">EA 23.278</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 20.64</t>
@@ -5906,7 +5906,7 @@
     <t xml:space="preserve">「它可以创造光与暗」</t>
   </si>
   <si>
-    <t xml:space="preserve">「将星光在提灯中点亮，伴随星屑的思念…」</t>
+    <t xml:space="preserve">「将星光在提灯中点亮，伴随星尘的思念…」</t>
   </si>
   <si>
     <t xml:space="preserve">「好严苛的客人啊」</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">1962</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">4982</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">1962</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">4982</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Backer.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">1962</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">4982</t>
